--- a/examples/demo_data/2026库存管理.xlsx
+++ b/examples/demo_data/2026库存管理.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>苏州包装厂</t>
+          <t>示例包装厂</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>广州办公设备</t>
+          <t>示例办公设备</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>苏州包装厂</t>
+          <t>示例包装厂</t>
         </is>
       </c>
     </row>
